--- a/results/job_matches_2026-05-19.xlsx
+++ b/results/job_matches_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - Active TS/SCI</t>
+          <t>Data and Insight Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Dataflow, Scala, Kafka</t>
+          <t>RDS, Databricks, Hadoop, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f872fe833e94e41d</t>
+          <t>https://www.indeed.com/viewjob?jk=bb46af131203645d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data and Insight Analyst</t>
+          <t>Data Engineer - Active TS/SCI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb46af131203645d</t>
+          <t>https://www.indeed.com/viewjob?jk=f872fe833e94e41d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Integration Developer, Senior</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03b8bbec4a94a31c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4ce7bf4011426a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Integration Developer, Senior</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VantageScore</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12497ac075998e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=03b8bbec4a94a31c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vanda Pharmaceuticals</t>
+          <t>VantageScore</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f51f479af9282287</t>
+          <t>https://www.indeed.com/viewjob?jk=12497ac075998e0b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Architect</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Vanda Pharmaceuticals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b7f11613741a49</t>
+          <t>https://www.indeed.com/viewjob?jk=f51f479af9282287</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa2e0e889ce30184</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2e59f6a4d8593c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2e59f6a4d8593c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa2e0e889ce30184</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Desmata Inc</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b018ddcc7ace0923</t>
+          <t>https://www.indeed.com/viewjob?jk=06078fce295ac913</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BIBA Practice - Big Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06078fce295ac913</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35842ddaad367b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BIBA Practice - Big Data Architect</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Desmata Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Data Lake Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35842ddaad367b</t>
+          <t>https://www.indeed.com/viewjob?jk=b018ddcc7ace0923</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>GoodRx</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861f927e60b04e75</t>
+          <t>https://www.indeed.com/viewjob?jk=9da3eb1c099fc483</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GoodRx</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da3eb1c099fc483</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5a60633917c610</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Engineer, IT Software</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1401,29 +1401,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5a60633917c610</t>
+          <t>https://www.indeed.com/viewjob?jk=af679155705e54bf</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer, IT Software</t>
+          <t>Front-end Programmer Developer - II or Senior</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Southwest Power Pool</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>S3, YARN, Scala, Oracle, MongoDB, ETL, Jenkins, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af679155705e54bf</t>
+          <t>https://www.indeed.com/viewjob?jk=ecef2fe2fa373cd8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4bcdd4cc1ef148d</t>
+          <t>https://www.indeed.com/viewjob?jk=861f927e60b04e75</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Front-end Programmer Developer - II or Senior</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Southwest Power Pool</t>
+          <t>RX USA LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Souderton, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>S3, YARN, Scala, Oracle, MongoDB, ETL, Jenkins, Kubernetes, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecef2fe2fa373cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6f69adb5e63bee</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Platform Engineer-US</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RX USA LLC</t>
+          <t>Certinia</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Souderton, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6f69adb5e63bee</t>
+          <t>https://www.indeed.com/viewjob?jk=ab574e0b18b6f234</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Platform Engineer-US</t>
+          <t>Data Platform Architect, AI Adoption</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Certinia</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab574e0b18b6f234</t>
+          <t>https://www.indeed.com/viewjob?jk=abf4cabe83b9851e</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Ledger Operations Engineer</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Airflow, Git</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76e3468c0010fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=be9f49babb6ca927</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Ledger Operations Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lentech Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
+          <t>Redshift, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326849a7cfebb04a</t>
+          <t>https://www.indeed.com/viewjob?jk=c76e3468c0010fc1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Harbinger Motors Inc.</t>
+          <t>Lentech Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Step Functions, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf02ed4b934745c</t>
+          <t>https://www.indeed.com/viewjob?jk=326849a7cfebb04a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IntegriChain</t>
+          <t>Harbinger Motors Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28193f1af5326eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf02ed4b934745c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>API Architect (Onsite Hybrid)</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>IntegriChain</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
+          <t>RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463679cc517d5924</t>
+          <t>https://www.indeed.com/viewjob?jk=28193f1af5326eaa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
+          <t>API Architect (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab39fae8644125cb</t>
+          <t>https://www.indeed.com/viewjob?jk=463679cc517d5924</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Security Software Engineer</t>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,19 +2246,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2a784d300f8363b</t>
+          <t>https://www.indeed.com/viewjob?jk=ab39fae8644125cb</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Senior DevSecOps / Security Engineer – Application &amp; Cloud (Ecommerce)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sevita</t>
+          <t>Thorne</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a46ce04515ea02</t>
+          <t>https://www.indeed.com/viewjob?jk=7f7be3e52d3af700</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>Microsoft Dynamics 365 Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
+          <t>ASPCA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Champaign, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,17 +2306,122 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1215e6b6c5c859a</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Security Software Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Electronic Arts</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2a784d300f8363b</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>University of Texas Health Science Center at San Antonio</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=03327cd0d2ff3bea</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Data Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Sevita</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50a46ce04515ea02</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-19.xlsx
+++ b/results/job_matches_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (Onsite)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>TCPWave</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b886774f2191937</t>
+          <t>https://www.indeed.com/viewjob?jk=3aa550f557c45270</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data and Insight Analyst</t>
+          <t>Senior IT Data Engineer (Onsite)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, PySpark, Scala, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb46af131203645d</t>
+          <t>https://www.indeed.com/viewjob?jk=7b886774f2191937</t>
         </is>
       </c>
     </row>
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AWS</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Encova Insurance</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86454c96969d5666</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2e59f6a4d8593c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2e59f6a4d8593c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa2e0e889ce30184</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Pharma Applications Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa2e0e889ce30184</t>
+          <t>https://www.indeed.com/viewjob?jk=f82dba2e1c1cad0d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MTSI</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd59b970d35a11e1</t>
+          <t>https://www.indeed.com/viewjob?jk=63a798e98d1f6f78</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pharma Applications Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, RDS, Azure, SQL Server, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82dba2e1c1cad0d</t>
+          <t>https://www.indeed.com/viewjob?jk=1eaa43d2708b0fa5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BCS Financial Corporation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63a798e98d1f6f78</t>
+          <t>https://www.indeed.com/viewjob?jk=16e946946005f3c9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data and AI Quality Automation Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BCS Financial Corporation</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MySQL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e946946005f3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=471e912481eed840</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data and AI Quality Automation Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>Bamboo Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MySQL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471e912481eed840</t>
+          <t>https://www.indeed.com/viewjob?jk=de8ea03efdc31e4c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bamboo Health</t>
+          <t>Pacific Consulting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8ea03efdc31e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=afb97449b7ed7b0d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer</t>
+          <t>BIBA Practice - Big Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MTSI</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Spark Streaming, Kafka, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d30e5165de2999c</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35842ddaad367b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MTSI</t>
+          <t>Desmata Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Spark Streaming, Kafka, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Lake Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe38a974a578c18</t>
+          <t>https://www.indeed.com/viewjob?jk=b018ddcc7ace0923</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DATA SCIENTIST</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>GoodRx</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Tableau, CI/CD, Git</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebb5de3ed4f3c295</t>
+          <t>https://www.indeed.com/viewjob?jk=9da3eb1c099fc483</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pacific Consulting</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb97449b7ed7b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5a60633917c610</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Front-end Programmer Developer - II or Senior</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Southwest Power Pool</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL</t>
+          <t>S3, YARN, Scala, Oracle, MongoDB, ETL, Jenkins, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06078fce295ac913</t>
+          <t>https://www.indeed.com/viewjob?jk=ecef2fe2fa373cd8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BIBA Practice - Big Data Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>RX USA LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Souderton, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35842ddaad367b</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6f69adb5e63bee</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Platform Engineer-US</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Desmata Inc</t>
+          <t>Certinia</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b018ddcc7ace0923</t>
+          <t>https://www.indeed.com/viewjob?jk=ab574e0b18b6f234</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GoodRx</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Docker, Kubernetes, AKS</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da3eb1c099fc483</t>
+          <t>https://www.indeed.com/viewjob?jk=8f633477012d7720</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bloomfield, CT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5a60633917c610</t>
+          <t>https://www.indeed.com/viewjob?jk=ac78439c3d5984bd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineer, IT Software</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af679155705e54bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a693f67199d64d3d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Front-end Programmer Developer - II or Senior</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Southwest Power Pool</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>S3, YARN, Scala, Oracle, MongoDB, ETL, Jenkins, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecef2fe2fa373cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=ab713a681fd0429b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861f927e60b04e75</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b99b8ea0db2061</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RX USA LLC</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Souderton, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6f69adb5e63bee</t>
+          <t>https://www.indeed.com/viewjob?jk=f5dc36c16524b514</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Platform Engineer-US</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Certinia</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab574e0b18b6f234</t>
+          <t>https://www.indeed.com/viewjob?jk=281daf9216f9080a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Platform Architect, AI Adoption</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf4cabe83b9851e</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ef5d5975efb63b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rockland Trust Company</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Bloomfield, CT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d4e78c9c5edc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=36c0fd77f8d43c48</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d474f9c4c5e446c7</t>
+          <t>https://www.indeed.com/viewjob?jk=15fa432a086d4c1f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Data Platform Architect, AI Adoption</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac78439c3d5984bd</t>
+          <t>https://www.indeed.com/viewjob?jk=abf4cabe83b9851e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a693f67199d64d3d</t>
+          <t>https://www.indeed.com/viewjob?jk=be9f49babb6ca927</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab713a681fd0429b</t>
+          <t>https://www.indeed.com/viewjob?jk=d474f9c4c5e446c7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Lentech Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Step Functions, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b99b8ea0db2061</t>
+          <t>https://www.indeed.com/viewjob?jk=326849a7cfebb04a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Harbinger Motors Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5dc36c16524b514</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf02ed4b934745c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>IntegriChain</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281daf9216f9080a</t>
+          <t>https://www.indeed.com/viewjob?jk=28193f1af5326eaa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Sr Engineer, Data Science &amp; Machine Learning Operations - remote opportunity</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Tivity Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Glue, Step Functions, S3, IAM, RDS, Scala, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ef5d5975efb63b</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba5979330da050e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Security Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36c0fd77f8d43c48</t>
+          <t>https://www.indeed.com/viewjob?jk=e2a784d300f8363b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fa432a086d4c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=ab39fae8644125cb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Sevita</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9f49babb6ca927</t>
+          <t>https://www.indeed.com/viewjob?jk=50a46ce04515ea02</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Ledger Operations Engineer</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Airflow, Git</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,357 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76e3468c0010fc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Lentech Inc.</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Fort Meade, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=326849a7cfebb04a</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Sr. Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Harbinger Motors Inc.</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Garden Grove, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf02ed4b934745c</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>IntegriChain</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28193f1af5326eaa</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>API Architect (Onsite Hybrid)</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=463679cc517d5924</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>ServiceTitan</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab39fae8644125cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Senior DevSecOps / Security Engineer – Application &amp; Cloud (Ecommerce)</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Thorne</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f7be3e52d3af700</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Microsoft Dynamics 365 Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>ASPCA</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Champaign, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1215e6b6c5c859a</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Security Software Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Electronic Arts</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2a784d300f8363b</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=03327cd0d2ff3bea</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Data Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Sevita</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50a46ce04515ea02</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-19.xlsx
+++ b/results/job_matches_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TCPWave</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aa550f557c45270</t>
+          <t>https://www.indeed.com/viewjob?jk=88dfefca6da19496</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (Onsite)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>TCPWave</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b886774f2191937</t>
+          <t>https://www.indeed.com/viewjob?jk=3aa550f557c45270</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer - Active TS/SCI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>SharkNinja</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Dataflow, Scala, Kafka</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f872fe833e94e41d</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb47d9c8a787444</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior IT Data Engineer (Onsite)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Willdan</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4ce7bf4011426a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b886774f2191937</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Integration Developer, Senior</t>
+          <t>Data Engineer- Local</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03b8bbec4a94a31c</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f567112b742a9e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer - Active TS/SCI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VantageScore</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12497ac075998e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f872fe833e94e41d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vanda Pharmaceuticals</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f51f479af9282287</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4ce7bf4011426a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>Data Integration Developer, Senior</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pax8</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb9ce5f60166ab4</t>
+          <t>https://www.indeed.com/viewjob?jk=03b8bbec4a94a31c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>VantageScore</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2e59f6a4d8593c</t>
+          <t>https://www.indeed.com/viewjob?jk=12497ac075998e0b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Vanda Pharmaceuticals</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa2e0e889ce30184</t>
+          <t>https://www.indeed.com/viewjob?jk=f51f479af9282287</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pharma Applications Engineer</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Pax8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,172 +846,172 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82dba2e1c1cad0d</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb9ce5f60166ab4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63a798e98d1f6f78</t>
+          <t>https://www.indeed.com/viewjob?jk=2f3215e173a2f079</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, RDS, Azure, SQL Server, DynamoDB, Splunk</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eaa43d2708b0fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=a35019214a98b077</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BCS Financial Corporation</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e946946005f3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=b9516aa524f738d9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data and AI Quality Automation Engineer</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MySQL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471e912481eed840</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5239019737c1e6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bamboo Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8ea03efdc31e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa2e0e889ce30184</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pacific Consulting</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb97449b7ed7b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2e59f6a4d8593c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BIBA Practice - Big Data Architect</t>
+          <t>Pharma Applications Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35842ddaad367b</t>
+          <t>https://www.indeed.com/viewjob?jk=f82dba2e1c1cad0d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Desmata Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b018ddcc7ace0923</t>
+          <t>https://www.indeed.com/viewjob?jk=63a798e98d1f6f78</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GoodRx</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Docker, Kubernetes, AKS</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, RDS, Azure, SQL Server, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da3eb1c099fc483</t>
+          <t>https://www.indeed.com/viewjob?jk=1eaa43d2708b0fa5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>BCS Financial Corporation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5a60633917c610</t>
+          <t>https://www.indeed.com/viewjob?jk=16e946946005f3c9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Front-end Programmer Developer - II or Senior</t>
+          <t>Data and AI Quality Automation Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Southwest Power Pool</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>S3, YARN, Scala, Oracle, MongoDB, ETL, Jenkins, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MySQL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecef2fe2fa373cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=471e912481eed840</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RX USA LLC</t>
+          <t>Bamboo Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Souderton, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6f69adb5e63bee</t>
+          <t>https://www.indeed.com/viewjob?jk=de8ea03efdc31e4c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Platform Engineer-US</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Certinia</t>
+          <t>Pacific Consulting</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab574e0b18b6f234</t>
+          <t>https://www.indeed.com/viewjob?jk=afb97449b7ed7b0d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Desmata Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Lake Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f633477012d7720</t>
+          <t>https://www.indeed.com/viewjob?jk=b018ddcc7ace0923</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>BIBA Practice - Big Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac78439c3d5984bd</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35842ddaad367b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>GoodRx</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a693f67199d64d3d</t>
+          <t>https://www.indeed.com/viewjob?jk=9da3eb1c099fc483</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab713a681fd0429b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5a60633917c610</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Front-end Programmer Developer - II or Senior</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Southwest Power Pool</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>S3, YARN, Scala, Oracle, MongoDB, ETL, Jenkins, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b99b8ea0db2061</t>
+          <t>https://www.indeed.com/viewjob?jk=ecef2fe2fa373cd8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5dc36c16524b514</t>
+          <t>https://www.indeed.com/viewjob?jk=a89ce09999706a8d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281daf9216f9080a</t>
+          <t>https://www.indeed.com/viewjob?jk=46f97f725c092d19</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ef5d5975efb63b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef6f778294e73998</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>RX USA LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>Souderton, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36c0fd77f8d43c48</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6f69adb5e63bee</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6ca2be8a3ba1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=8f633477012d7720</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Bloomfield, CT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fa432a086d4c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=ac78439c3d5984bd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Platform Architect, AI Adoption</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf4cabe83b9851e</t>
+          <t>https://www.indeed.com/viewjob?jk=a693f67199d64d3d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9f49babb6ca927</t>
+          <t>https://www.indeed.com/viewjob?jk=ab713a681fd0429b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d474f9c4c5e446c7</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b99b8ea0db2061</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lentech Inc.</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326849a7cfebb04a</t>
+          <t>https://www.indeed.com/viewjob?jk=f5dc36c16524b514</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Harbinger Motors Inc.</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf02ed4b934745c</t>
+          <t>https://www.indeed.com/viewjob?jk=281daf9216f9080a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IntegriChain</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28193f1af5326eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ef5d5975efb63b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Science &amp; Machine Learning Operations - remote opportunity</t>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tivity Health</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomfield, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, IAM, RDS, Scala, ETL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba5979330da050e</t>
+          <t>https://www.indeed.com/viewjob?jk=36c0fd77f8d43c48</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Security Software Engineer</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2a784d300f8363b</t>
+          <t>https://www.indeed.com/viewjob?jk=5a6ca2be8a3ba1c4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,42 +2001,42 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab39fae8644125cb</t>
+          <t>https://www.indeed.com/viewjob?jk=15fa432a086d4c1f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Data Platform Architect, AI Adoption</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sevita</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a46ce04515ea02</t>
+          <t>https://www.indeed.com/viewjob?jk=abf4cabe83b9851e</t>
         </is>
       </c>
     </row>
@@ -2048,30 +2048,380 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>UT Health Science Center at San Antonio</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be9f49babb6ca927</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Database Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d474f9c4c5e446c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Lentech Inc.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=326849a7cfebb04a</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Sr. Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Harbinger Motors Inc.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Garden Grove, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cf02ed4b934745c</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>IntegriChain</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28193f1af5326eaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Sr Engineer, Data Science &amp; Machine Learning Operations - remote opportunity</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Tivity Health</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Step Functions, S3, IAM, RDS, Scala, ETL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ba5979330da050e</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Security Software Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Electronic Arts</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2a784d300f8363b</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ServiceTitan</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab39fae8644125cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Data Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Sevita</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50a46ce04515ea02</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>San Antonio, TX, US USA</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D56" t="n">
         <v>10.4</v>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=03327cd0d2ff3bea</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Solution Engineer: Enterprise GenAI &amp; Analytics Enablement</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>American Electric Power</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9df419a67df1ba59</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-19.xlsx
+++ b/results/job_matches_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TCPWave</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Township of Jackson, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aa550f557c45270</t>
+          <t>https://www.indeed.com/viewjob?jk=6caaa34875b1debe</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SharkNinja</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,77 +556,77 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb47d9c8a787444</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b79cbd12020dac</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (Onsite)</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b886774f2191937</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d6b6fd4abcdced</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer- Local</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>TCPWave</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f567112b742a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=3aa550f557c45270</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - Active TS/SCI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>SharkNinja</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Dataflow, Scala, Kafka</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f872fe833e94e41d</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb47d9c8a787444</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer- Local</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Willdan</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4ce7bf4011426a</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f567112b742a9e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Integration Developer, Senior</t>
+          <t>Senior IT Data Engineer (Onsite)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03b8bbec4a94a31c</t>
+          <t>https://www.indeed.com/viewjob?jk=7b886774f2191937</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer - Active TS/SCI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VantageScore</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12497ac075998e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f872fe833e94e41d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vanda Pharmaceuticals</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f51f479af9282287</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4ce7bf4011426a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>Data Integration Developer, Senior</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pax8</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,94 +846,94 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb9ce5f60166ab4</t>
+          <t>https://www.indeed.com/viewjob?jk=03b8bbec4a94a31c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>VantageScore</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f3215e173a2f079</t>
+          <t>https://www.indeed.com/viewjob?jk=12497ac075998e0b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Vanda Pharmaceuticals</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35019214a98b077</t>
+          <t>https://www.indeed.com/viewjob?jk=f51f479af9282287</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9516aa524f738d9</t>
+          <t>https://www.indeed.com/viewjob?jk=154aec3c659c637e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5239019737c1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=7b763ccac8082bb3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Pax8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,207 +1021,207 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa2e0e889ce30184</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb9ce5f60166ab4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>.NET Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2e59f6a4d8593c</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e4611f2709de72</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pharma Applications Engineer</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82dba2e1c1cad0d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f3215e173a2f079</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63a798e98d1f6f78</t>
+          <t>https://www.indeed.com/viewjob?jk=a35019214a98b077</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, RDS, Azure, SQL Server, DynamoDB, Splunk</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eaa43d2708b0fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=b9516aa524f738d9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BCS Financial Corporation</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e946946005f3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5239019737c1e6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data and AI Quality Automation Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MySQL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471e912481eed840</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2e59f6a4d8593c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bamboo Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,19 +1266,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8ea03efdc31e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa2e0e889ce30184</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pacific Consulting</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1287,46 +1287,46 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb97449b7ed7b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=688d23a37649aa4e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Pharma Applications Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Desmata Inc</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,54 +1336,54 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b018ddcc7ace0923</t>
+          <t>https://www.indeed.com/viewjob?jk=f82dba2e1c1cad0d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BIBA Practice - Big Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35842ddaad367b</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c6986e7938de04</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Intregration Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GoodRx</t>
+          <t>IntegraTouch</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1392,46 +1392,46 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, Azure, GCP, Cloud Storage, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da3eb1c099fc483</t>
+          <t>https://www.indeed.com/viewjob?jk=189b52949d35286b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5a60633917c610</t>
+          <t>https://www.indeed.com/viewjob?jk=63a798e98d1f6f78</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Front-end Programmer Developer - II or Senior</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Southwest Power Pool</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>S3, YARN, Scala, Oracle, MongoDB, ETL, Jenkins, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, RDS, Azure, SQL Server, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecef2fe2fa373cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=1eaa43d2708b0fa5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89ce09999706a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=a198e2f00d09e497</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f97f725c092d19</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5897cf20f4924d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6f778294e73998</t>
+          <t>https://www.indeed.com/viewjob?jk=6add22c42e86ee8d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RX USA LLC</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Souderton, PA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6f69adb5e63bee</t>
+          <t>https://www.indeed.com/viewjob?jk=060e90baddbaabb6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,382 +1651,382 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f633477012d7720</t>
+          <t>https://www.indeed.com/viewjob?jk=29fa15772fc8215e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac78439c3d5984bd</t>
+          <t>https://www.indeed.com/viewjob?jk=dbeaf5356928be79</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a693f67199d64d3d</t>
+          <t>https://www.indeed.com/viewjob?jk=30aac5b70ec21742</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab713a681fd0429b</t>
+          <t>https://www.indeed.com/viewjob?jk=e1224f39b4d10142</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b99b8ea0db2061</t>
+          <t>https://www.indeed.com/viewjob?jk=8b20c6e56d2f2685</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5dc36c16524b514</t>
+          <t>https://www.indeed.com/viewjob?jk=57de84d9a0a356fd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281daf9216f9080a</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7a4bbc97a4a7bf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ef5d5975efb63b</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0d1d3131f74e61</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36c0fd77f8d43c48</t>
+          <t>https://www.indeed.com/viewjob?jk=99acdc5f038ec993</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6ca2be8a3ba1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=417fe7ce0dd45b13</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fa432a086d4c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba18545223c64cb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Platform Architect, AI Adoption</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,392 +2036,2457 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf4cabe83b9851e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b7609618f1bb60b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9f49babb6ca927</t>
+          <t>https://www.indeed.com/viewjob?jk=42786522a873fac5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d474f9c4c5e446c7</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1e37739c6d4489</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lentech Inc.</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326849a7cfebb04a</t>
+          <t>https://www.indeed.com/viewjob?jk=4837b9e4911393cf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Harbinger Motors Inc.</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf02ed4b934745c</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7ab2808448b848</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IntegriChain</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28193f1af5326eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=c440af126bc87e6f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Science &amp; Machine Learning Operations - remote opportunity</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tivity Health</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, IAM, RDS, Scala, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba5979330da050e</t>
+          <t>https://www.indeed.com/viewjob?jk=8aed0004eb1e73c2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Security Software Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2a784d300f8363b</t>
+          <t>https://www.indeed.com/viewjob?jk=58e007bbdf452d21</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab39fae8644125cb</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b4f9cd182d1098</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sevita</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a46ce04515ea02</t>
+          <t>https://www.indeed.com/viewjob?jk=10812a5dd633ba29</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Ketchikan, AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03327cd0d2ff3bea</t>
+          <t>https://www.indeed.com/viewjob?jk=5cbc2599ef10ec38</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Solution Engineer: Enterprise GenAI &amp; Analytics Enablement</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d3c03923d226d6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CT, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f0c53177d376165</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>NE, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cb2d6450935c77c</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2139a4cc82cf98d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ND, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84ec6e1b6a41c09d</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90a8660d20e3925c</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea946bc190711225</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AR, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79a44a6e66a933e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5df6fdfb75f5432d</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>NH, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9aa599a96ed4d6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Santa Ana, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68cdb549def54218</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>WY, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7272f84ff6357152</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52db1fcf17eb0ef7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e02b0fedb5c9b46f</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>NV, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9ccfe1a1c1f3d82</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96157e562b62f43b</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fcfbe3b324a53aa8</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>VT, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdb0f2907c4f113d</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>IA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81bfbbc916c4bf3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae070dd661915e6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>OK, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=836c940883a7c623</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SC, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9623f5aff1bc8e49</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d05fef2d9ced9478</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>DE, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2d976dafe088343</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BCS Financial Corporation</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Oakbrook Terrace, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16e946946005f3c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Data and AI Quality Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Stratus</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MySQL, ELT</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=471e912481eed840</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Bamboo Health</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de8ea03efdc31e4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Pacific Consulting</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afb97449b7ed7b0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BIBA Practice - Big Data Architect</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Hexaware Technologies</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a35842ddaad367b</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Azure Data Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Desmata Inc</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Texas City, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Lake Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b018ddcc7ace0923</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>GoodRx</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9da3eb1c099fc483</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b5a60633917c610</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Oracle Unity/Fusion Customer Data Platform (CDP) Developer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Hashout Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05820054e138dd33</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Santa Monica, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a89ce09999706a8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46f97f725c092d19</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef6f778294e73998</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior .net Software Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f633477012d7720</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sr Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Hertz</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a6ca2be8a3ba1c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>OnMed</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>White Plains, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15fa432a086d4c1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Bloomfield, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac78439c3d5984bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a693f67199d64d3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Morris Plains, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab713a681fd0429b</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8b99b8ea0db2061</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5dc36c16524b514</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Bloomington, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=281daf9216f9080a</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1ef5d5975efb63b</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Data Platform Architect, AI Adoption</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abf4cabe83b9851e</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>UT Health Science Center at San Antonio</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be9f49babb6ca927</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Database Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d474f9c4c5e446c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior AI &amp; Data Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Alamar Biosciences</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Fremont, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
         <v>10.4</v>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9df419a67df1ba59</t>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>ECS, RDS, Databricks, Unity Catalog, BigQuery, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1884155644ac6742</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Lentech Inc.</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=326849a7cfebb04a</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Sr. Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Harbinger Motors Inc.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Garden Grove, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cf02ed4b934745c</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Database Administrator (New York, NY - US)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Energy Solutions</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Python</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d13c0f429a80b43</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Database Administrator (Portland, OR - US)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Energy Solutions</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Python</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1df1dc65f5bf751b</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Database Administrator (Chicago, IL- US)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Energy Solutions</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Python</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb65af8c43f9fc32</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Database Administrator (Orange, CA - US)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Energy Solutions</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Orange, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Python</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=505e60955729c7b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Database Administrator (Boston,MA - US)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Energy Solutions</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Python</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21538c437c55ec26</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Database Administrator (Oakland, CA - US)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Energy Solutions</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Python</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cadff332c22c58a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ServiceTitan</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab39fae8644125cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Data Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Sevita</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50a46ce04515ea02</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-19.xlsx
+++ b/results/job_matches_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data &amp; Analytics Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>L.E.K. Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88dfefca6da19496</t>
+          <t>https://www.indeed.com/viewjob?jk=9ddcbcd3fcf90b62</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Township of Jackson, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6caaa34875b1debe</t>
+          <t>https://www.indeed.com/viewjob?jk=88dfefca6da19496</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>SharkNinja</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b79cbd12020dac</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb47d9c8a787444</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>TCPWave</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d6b6fd4abcdced</t>
+          <t>https://www.indeed.com/viewjob?jk=3aa550f557c45270</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer- Local</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TCPWave</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aa550f557c45270</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f567112b742a9e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior IT Data Engineer (Onsite)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SharkNinja</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb47d9c8a787444</t>
+          <t>https://www.indeed.com/viewjob?jk=7b886774f2191937</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer- Local</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, GCP, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f567112b742a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=9c24ee3772fb2025</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (Onsite)</t>
+          <t>Senior Data Engineer - Quality</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b886774f2191937</t>
+          <t>https://www.indeed.com/viewjob?jk=6913762be867dbf6</t>
         </is>
       </c>
     </row>
@@ -888,35 +888,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vanda Pharmaceuticals</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f51f479af9282287</t>
+          <t>https://www.indeed.com/viewjob?jk=154aec3c659c637e</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154aec3c659c637e</t>
+          <t>https://www.indeed.com/viewjob?jk=7b763ccac8082bb3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Pax8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b763ccac8082bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb9ce5f60166ab4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pax8</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb9ce5f60166ab4</t>
+          <t>https://www.indeed.com/viewjob?jk=2f3215e173a2f079</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>.NET Architect</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e4611f2709de72</t>
+          <t>https://www.indeed.com/viewjob?jk=a35019214a98b077</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f3215e173a2f079</t>
+          <t>https://www.indeed.com/viewjob?jk=b9516aa524f738d9</t>
         </is>
       </c>
     </row>
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35019214a98b077</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5239019737c1e6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9516aa524f738d9</t>
+          <t>https://www.indeed.com/viewjob?jk=46cdeb4b1af72885</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5239019737c1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=688d23a37649aa4e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Pharma Applications Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2e59f6a4d8593c</t>
+          <t>https://www.indeed.com/viewjob?jk=f82dba2e1c1cad0d</t>
         </is>
       </c>
     </row>
@@ -1243,55 +1243,55 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa2e0e889ce30184</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c6986e7938de04</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Intregration Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>IntegraTouch</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Cloud Storage, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688d23a37649aa4e</t>
+          <t>https://www.indeed.com/viewjob?jk=189b52949d35286b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pharma Applications Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82dba2e1c1cad0d</t>
+          <t>https://www.indeed.com/viewjob?jk=63a798e98d1f6f78</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, RDS, Azure, SQL Server, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c6986e7938de04</t>
+          <t>https://www.indeed.com/viewjob?jk=1eaa43d2708b0fa5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Intregration Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IntegraTouch</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Cloud Storage, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,77 +1406,77 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189b52949d35286b</t>
+          <t>https://www.indeed.com/viewjob?jk=a198e2f00d09e497</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63a798e98d1f6f78</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5897cf20f4924d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, RDS, Azure, SQL Server, DynamoDB, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eaa43d2708b0fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=6add22c42e86ee8d</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a198e2f00d09e497</t>
+          <t>https://www.indeed.com/viewjob?jk=060e90baddbaabb6</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5897cf20f4924d</t>
+          <t>https://www.indeed.com/viewjob?jk=29fa15772fc8215e</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6add22c42e86ee8d</t>
+          <t>https://www.indeed.com/viewjob?jk=dbeaf5356928be79</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=060e90baddbaabb6</t>
+          <t>https://www.indeed.com/viewjob?jk=30aac5b70ec21742</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fa15772fc8215e</t>
+          <t>https://www.indeed.com/viewjob?jk=e1224f39b4d10142</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbeaf5356928be79</t>
+          <t>https://www.indeed.com/viewjob?jk=8b20c6e56d2f2685</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30aac5b70ec21742</t>
+          <t>https://www.indeed.com/viewjob?jk=57de84d9a0a356fd</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1224f39b4d10142</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7a4bbc97a4a7bf</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b20c6e56d2f2685</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0d1d3131f74e61</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57de84d9a0a356fd</t>
+          <t>https://www.indeed.com/viewjob?jk=99acdc5f038ec993</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7a4bbc97a4a7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=417fe7ce0dd45b13</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0d1d3131f74e61</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba18545223c64cb</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99acdc5f038ec993</t>
+          <t>https://www.indeed.com/viewjob?jk=0b7609618f1bb60b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417fe7ce0dd45b13</t>
+          <t>https://www.indeed.com/viewjob?jk=42786522a873fac5</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba18545223c64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1e37739c6d4489</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b7609618f1bb60b</t>
+          <t>https://www.indeed.com/viewjob?jk=4837b9e4911393cf</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42786522a873fac5</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7ab2808448b848</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1e37739c6d4489</t>
+          <t>https://www.indeed.com/viewjob?jk=c440af126bc87e6f</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4837b9e4911393cf</t>
+          <t>https://www.indeed.com/viewjob?jk=8aed0004eb1e73c2</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7ab2808448b848</t>
+          <t>https://www.indeed.com/viewjob?jk=58e007bbdf452d21</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c440af126bc87e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b4f9cd182d1098</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aed0004eb1e73c2</t>
+          <t>https://www.indeed.com/viewjob?jk=10812a5dd633ba29</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Ketchikan, AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e007bbdf452d21</t>
+          <t>https://www.indeed.com/viewjob?jk=5cbc2599ef10ec38</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b4f9cd182d1098</t>
+          <t>https://www.indeed.com/viewjob?jk=3d3c03923d226d6f</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10812a5dd633ba29</t>
+          <t>https://www.indeed.com/viewjob?jk=5f0c53177d376165</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ketchikan, AK, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cbc2599ef10ec38</t>
+          <t>https://www.indeed.com/viewjob?jk=6cb2d6450935c77c</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d3c03923d226d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=2139a4cc82cf98d5</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f0c53177d376165</t>
+          <t>https://www.indeed.com/viewjob?jk=84ec6e1b6a41c09d</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb2d6450935c77c</t>
+          <t>https://www.indeed.com/viewjob?jk=90a8660d20e3925c</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2139a4cc82cf98d5</t>
+          <t>https://www.indeed.com/viewjob?jk=ea946bc190711225</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec6e1b6a41c09d</t>
+          <t>https://www.indeed.com/viewjob?jk=79a44a6e66a933e3</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a8660d20e3925c</t>
+          <t>https://www.indeed.com/viewjob?jk=5df6fdfb75f5432d</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea946bc190711225</t>
+          <t>https://www.indeed.com/viewjob?jk=c9aa599a96ed4d6c</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a44a6e66a933e3</t>
+          <t>https://www.indeed.com/viewjob?jk=68cdb549def54218</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df6fdfb75f5432d</t>
+          <t>https://www.indeed.com/viewjob?jk=7272f84ff6357152</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9aa599a96ed4d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=52db1fcf17eb0ef7</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68cdb549def54218</t>
+          <t>https://www.indeed.com/viewjob?jk=e02b0fedb5c9b46f</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7272f84ff6357152</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ccfe1a1c1f3d82</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52db1fcf17eb0ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=96157e562b62f43b</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02b0fedb5c9b46f</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfbe3b324a53aa8</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ccfe1a1c1f3d82</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb0f2907c4f113d</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96157e562b62f43b</t>
+          <t>https://www.indeed.com/viewjob?jk=81bfbbc916c4bf3d</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfbe3b324a53aa8</t>
+          <t>https://www.indeed.com/viewjob?jk=ae070dd661915e6c</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb0f2907c4f113d</t>
+          <t>https://www.indeed.com/viewjob?jk=836c940883a7c623</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81bfbbc916c4bf3d</t>
+          <t>https://www.indeed.com/viewjob?jk=9623f5aff1bc8e49</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae070dd661915e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=d05fef2d9ced9478</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=836c940883a7c623</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d976dafe088343</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>BCS Financial Corporation</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9623f5aff1bc8e49</t>
+          <t>https://www.indeed.com/viewjob?jk=16e946946005f3c9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Data and AI Quality Automation Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MySQL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05fef2d9ced9478</t>
+          <t>https://www.indeed.com/viewjob?jk=471e912481eed840</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Bamboo Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d976dafe088343</t>
+          <t>https://www.indeed.com/viewjob?jk=de8ea03efdc31e4c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BCS Financial Corporation</t>
+          <t>Pacific Consulting</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e946946005f3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=afb97449b7ed7b0d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data and AI Quality Automation Engineer</t>
+          <t>BIBA Practice - Big Data Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MySQL, ELT</t>
+          <t>AWS, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471e912481eed840</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35842ddaad367b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bamboo Health</t>
+          <t>Desmata Inc</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Lake Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8ea03efdc31e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=b018ddcc7ace0923</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pacific Consulting</t>
+          <t>GoodRx</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb97449b7ed7b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=9da3eb1c099fc483</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BIBA Practice - Big Data Architect</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35842ddaad367b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5a60633917c610</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Oracle Unity/Fusion Customer Data Platform (CDP) Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Desmata Inc</t>
+          <t>Hashout Technologies, Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,112 +3426,112 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b018ddcc7ace0923</t>
+          <t>https://www.indeed.com/viewjob?jk=05820054e138dd33</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GoodRx</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Docker, Kubernetes, AKS</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da3eb1c099fc483</t>
+          <t>https://www.indeed.com/viewjob?jk=a89ce09999706a8d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5a60633917c610</t>
+          <t>https://www.indeed.com/viewjob?jk=46f97f725c092d19</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Oracle Unity/Fusion Customer Data Platform (CDP) Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Hashout Technologies, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05820054e138dd33</t>
+          <t>https://www.indeed.com/viewjob?jk=ef6f778294e73998</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Salesforce Enterprise Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Purple Austyn Technologies</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89ce09999706a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef8a774183b65cc</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f97f725c092d19</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f1526a2cc9c583</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6f778294e73998</t>
+          <t>https://www.indeed.com/viewjob?jk=8f633477012d7720</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f633477012d7720</t>
+          <t>https://www.indeed.com/viewjob?jk=5a6ca2be8a3ba1c4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6ca2be8a3ba1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=66f736568439fa09</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Maven, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fa432a086d4c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=d38e83f9c27ee7f1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac78439c3d5984bd</t>
+          <t>https://www.indeed.com/viewjob?jk=b1b55ac084d2b38e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a693f67199d64d3d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bedeff840282078</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab713a681fd0429b</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d440465d091eb4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Data Platform Architect, AI Adoption</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b99b8ea0db2061</t>
+          <t>https://www.indeed.com/viewjob?jk=abf4cabe83b9851e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5dc36c16524b514</t>
+          <t>https://www.indeed.com/viewjob?jk=be9f49babb6ca927</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,67 +3961,67 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281daf9216f9080a</t>
+          <t>https://www.indeed.com/viewjob?jk=d474f9c4c5e446c7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor – Data Engineer - Hybrid</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>RA Capital Management</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Scala, Dimensional Modeling, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ef5d5975efb63b</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb511c116964595</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Platform Architect, AI Adoption</t>
+          <t>Senior AI &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Alamar Biosciences</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes</t>
+          <t>ECS, RDS, Databricks, Unity Catalog, BigQuery, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf4cabe83b9851e</t>
+          <t>https://www.indeed.com/viewjob?jk=1884155644ac6742</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Lentech Inc.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, Lambda, Step Functions, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9f49babb6ca927</t>
+          <t>https://www.indeed.com/viewjob?jk=326849a7cfebb04a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Harbinger Motors Inc.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d474f9c4c5e446c7</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf02ed4b934745c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Alamar Biosciences</t>
+          <t>Genesys</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Unity Catalog, BigQuery, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, IAM, Scala, DynamoDB, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1884155644ac6742</t>
+          <t>https://www.indeed.com/viewjob?jk=be2a8db8df79df5f</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Aerospace Software DevOps Engineer II</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Lentech Inc.</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326849a7cfebb04a</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b1191705b29853</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Harbinger Motors Inc.</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,287 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf02ed4b934745c</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Database Administrator (New York, NY - US)</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Energy Solutions</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Python</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d13c0f429a80b43</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Database Administrator (Portland, OR - US)</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Energy Solutions</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Python</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1df1dc65f5bf751b</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Database Administrator (Chicago, IL- US)</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Energy Solutions</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Python</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb65af8c43f9fc32</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Database Administrator (Orange, CA - US)</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Energy Solutions</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Orange, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Python</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=505e60955729c7b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Database Administrator (Boston,MA - US)</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Energy Solutions</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Python</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21538c437c55ec26</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Database Administrator (Oakland, CA - US)</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Energy Solutions</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, Power BI, Tableau, Python</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cadff332c22c58a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>ServiceTitan</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=ab39fae8644125cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Data Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Sevita</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Kafka Connect, Snowflake, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50a46ce04515ea02</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-19.xlsx
+++ b/results/job_matches_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer- Local</t>
+          <t>Senior IT Data Engineer (Onsite)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f567112b742a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=7b886774f2191937</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (Onsite)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, GCP, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b886774f2191937</t>
+          <t>https://www.indeed.com/viewjob?jk=9c24ee3772fb2025</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer- Local</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sidley Austin</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, GCP, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c24ee3772fb2025</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f567112b742a9e</t>
         </is>
       </c>
     </row>
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - Active TS/SCI</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Dataflow, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f872fe833e94e41d</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4ce7bf4011426a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Integration Developer, Senior</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Willdan</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4ce7bf4011426a</t>
+          <t>https://www.indeed.com/viewjob?jk=03b8bbec4a94a31c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Integration Developer, Senior</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>VantageScore</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03b8bbec4a94a31c</t>
+          <t>https://www.indeed.com/viewjob?jk=12497ac075998e0b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AI Full Stack Developer &amp; Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VantageScore</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, CI/CD</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12497ac075998e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=1245fb4aa0b33840</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Forward Deployed Engineer (Foundry)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Trinity Industries</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154aec3c659c637e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1207216093eb19</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b763ccac8082bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=154aec3c659c637e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pax8</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb9ce5f60166ab4</t>
+          <t>https://www.indeed.com/viewjob?jk=7b763ccac8082bb3</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, RDS, Azure, SQL Server, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,42 +1336,42 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63a798e98d1f6f78</t>
+          <t>https://www.indeed.com/viewjob?jk=1eaa43d2708b0fa5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, RDS, Azure, SQL Server, DynamoDB, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eaa43d2708b0fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=a198e2f00d09e497</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a198e2f00d09e497</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5897cf20f4924d</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5897cf20f4924d</t>
+          <t>https://www.indeed.com/viewjob?jk=6add22c42e86ee8d</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6add22c42e86ee8d</t>
+          <t>https://www.indeed.com/viewjob?jk=060e90baddbaabb6</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=060e90baddbaabb6</t>
+          <t>https://www.indeed.com/viewjob?jk=29fa15772fc8215e</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fa15772fc8215e</t>
+          <t>https://www.indeed.com/viewjob?jk=dbeaf5356928be79</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbeaf5356928be79</t>
+          <t>https://www.indeed.com/viewjob?jk=30aac5b70ec21742</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30aac5b70ec21742</t>
+          <t>https://www.indeed.com/viewjob?jk=e1224f39b4d10142</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1224f39b4d10142</t>
+          <t>https://www.indeed.com/viewjob?jk=8b20c6e56d2f2685</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b20c6e56d2f2685</t>
+          <t>https://www.indeed.com/viewjob?jk=57de84d9a0a356fd</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57de84d9a0a356fd</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7a4bbc97a4a7bf</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7a4bbc97a4a7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0d1d3131f74e61</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0d1d3131f74e61</t>
+          <t>https://www.indeed.com/viewjob?jk=99acdc5f038ec993</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99acdc5f038ec993</t>
+          <t>https://www.indeed.com/viewjob?jk=417fe7ce0dd45b13</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417fe7ce0dd45b13</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba18545223c64cb</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba18545223c64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=0b7609618f1bb60b</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b7609618f1bb60b</t>
+          <t>https://www.indeed.com/viewjob?jk=42786522a873fac5</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42786522a873fac5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1e37739c6d4489</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1e37739c6d4489</t>
+          <t>https://www.indeed.com/viewjob?jk=4837b9e4911393cf</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4837b9e4911393cf</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7ab2808448b848</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7ab2808448b848</t>
+          <t>https://www.indeed.com/viewjob?jk=c440af126bc87e6f</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c440af126bc87e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=8aed0004eb1e73c2</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aed0004eb1e73c2</t>
+          <t>https://www.indeed.com/viewjob?jk=58e007bbdf452d21</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e007bbdf452d21</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b4f9cd182d1098</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b4f9cd182d1098</t>
+          <t>https://www.indeed.com/viewjob?jk=10812a5dd633ba29</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Ketchikan, AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10812a5dd633ba29</t>
+          <t>https://www.indeed.com/viewjob?jk=5cbc2599ef10ec38</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ketchikan, AK, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cbc2599ef10ec38</t>
+          <t>https://www.indeed.com/viewjob?jk=3d3c03923d226d6f</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d3c03923d226d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=5f0c53177d376165</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f0c53177d376165</t>
+          <t>https://www.indeed.com/viewjob?jk=6cb2d6450935c77c</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb2d6450935c77c</t>
+          <t>https://www.indeed.com/viewjob?jk=2139a4cc82cf98d5</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2139a4cc82cf98d5</t>
+          <t>https://www.indeed.com/viewjob?jk=84ec6e1b6a41c09d</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec6e1b6a41c09d</t>
+          <t>https://www.indeed.com/viewjob?jk=90a8660d20e3925c</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a8660d20e3925c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea946bc190711225</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea946bc190711225</t>
+          <t>https://www.indeed.com/viewjob?jk=79a44a6e66a933e3</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a44a6e66a933e3</t>
+          <t>https://www.indeed.com/viewjob?jk=5df6fdfb75f5432d</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df6fdfb75f5432d</t>
+          <t>https://www.indeed.com/viewjob?jk=c9aa599a96ed4d6c</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9aa599a96ed4d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=68cdb549def54218</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68cdb549def54218</t>
+          <t>https://www.indeed.com/viewjob?jk=7272f84ff6357152</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7272f84ff6357152</t>
+          <t>https://www.indeed.com/viewjob?jk=52db1fcf17eb0ef7</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52db1fcf17eb0ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=e02b0fedb5c9b46f</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02b0fedb5c9b46f</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ccfe1a1c1f3d82</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ccfe1a1c1f3d82</t>
+          <t>https://www.indeed.com/viewjob?jk=96157e562b62f43b</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96157e562b62f43b</t>
+          <t>https://www.indeed.com/viewjob?jk=fcfbe3b324a53aa8</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfbe3b324a53aa8</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb0f2907c4f113d</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb0f2907c4f113d</t>
+          <t>https://www.indeed.com/viewjob?jk=81bfbbc916c4bf3d</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81bfbbc916c4bf3d</t>
+          <t>https://www.indeed.com/viewjob?jk=ae070dd661915e6c</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae070dd661915e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=836c940883a7c623</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=836c940883a7c623</t>
+          <t>https://www.indeed.com/viewjob?jk=9623f5aff1bc8e49</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9623f5aff1bc8e49</t>
+          <t>https://www.indeed.com/viewjob?jk=d05fef2d9ced9478</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05fef2d9ced9478</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d976dafe088343</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>BCS Financial Corporation</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d976dafe088343</t>
+          <t>https://www.indeed.com/viewjob?jk=16e946946005f3c9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data and AI Quality Automation Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BCS Financial Corporation</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MySQL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e946946005f3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=471e912481eed840</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data and AI Quality Automation Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>Success Academy Charter Schools</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MySQL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471e912481eed840</t>
+          <t>https://www.indeed.com/viewjob?jk=f69cae0b073ffd83</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bamboo Health</t>
+          <t>Pacific Consulting</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8ea03efdc31e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=afb97449b7ed7b0d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pacific Consulting</t>
+          <t>Desmata Inc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Lake Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb97449b7ed7b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=b018ddcc7ace0923</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Desmata Inc</t>
+          <t>GoodRx</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,19 +3331,19 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b018ddcc7ace0923</t>
+          <t>https://www.indeed.com/viewjob?jk=9da3eb1c099fc483</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Oracle Unity/Fusion Customer Data Platform (CDP) Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GoodRx</t>
+          <t>Hashout Technologies, Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3356,77 +3356,77 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da3eb1c099fc483</t>
+          <t>https://www.indeed.com/viewjob?jk=05820054e138dd33</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5a60633917c610</t>
+          <t>https://www.indeed.com/viewjob?jk=4de6845b355390df</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Oracle Unity/Fusion Customer Data Platform (CDP) Developer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Hashout Technologies, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05820054e138dd33</t>
+          <t>https://www.indeed.com/viewjob?jk=a89ce09999706a8d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89ce09999706a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=46f97f725c092d19</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f97f725c092d19</t>
+          <t>https://www.indeed.com/viewjob?jk=ef6f778294e73998</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Salesforce Enterprise Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Purple Austyn Technologies</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6f778294e73998</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef8a774183b65cc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Salesforce Enterprise Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Purple Austyn Technologies</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef8a774183b65cc</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f1526a2cc9c583</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f1526a2cc9c583</t>
+          <t>https://www.indeed.com/viewjob?jk=8f633477012d7720</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f633477012d7720</t>
+          <t>https://www.indeed.com/viewjob?jk=5a6ca2be8a3ba1c4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6ca2be8a3ba1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=66f736568439fa09</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f736568439fa09</t>
+          <t>https://www.indeed.com/viewjob?jk=d38e83f9c27ee7f1</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38e83f9c27ee7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=b1b55ac084d2b38e</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1b55ac084d2b38e</t>
+          <t>https://www.indeed.com/viewjob?jk=8bedeff840282078</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bedeff840282078</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d440465d091eb4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Platform Architect, AI Adoption</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d440465d091eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=abf4cabe83b9851e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Platform Architect, AI Adoption</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf4cabe83b9851e</t>
+          <t>https://www.indeed.com/viewjob?jk=be9f49babb6ca927</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,59 +3926,59 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9f49babb6ca927</t>
+          <t>https://www.indeed.com/viewjob?jk=d474f9c4c5e446c7</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>RA Capital Management</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d474f9c4c5e446c7</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb511c116964595</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Senior AI &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>RA Capital Management</t>
+          <t>Alamar Biosciences</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>ECS, RDS, Databricks, Unity Catalog, BigQuery, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb511c116964595</t>
+          <t>https://www.indeed.com/viewjob?jk=1884155644ac6742</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Alamar Biosciences</t>
+          <t>Lentech Inc.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Unity Catalog, BigQuery, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Step Functions, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1884155644ac6742</t>
+          <t>https://www.indeed.com/viewjob?jk=326849a7cfebb04a</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Lentech Inc.</t>
+          <t>Harbinger Motors Inc.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326849a7cfebb04a</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf02ed4b934745c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Harbinger Motors Inc.</t>
+          <t>Genesys</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, IAM, Scala, DynamoDB, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf02ed4b934745c</t>
+          <t>https://www.indeed.com/viewjob?jk=be2a8db8df79df5f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Aerospace Software DevOps Engineer II</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Genesys</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, IAM, Scala, DynamoDB, Jenkins, Maven, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be2a8db8df79df5f</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b1191705b29853</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Aerospace Software DevOps Engineer II</t>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,50 +4161,15 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b1191705b29853</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>ServiceTitan</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ab39fae8644125cb</t>
         </is>

--- a/results/job_matches_2026-05-19.xlsx
+++ b/results/job_matches_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (Onsite)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, GCP, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b886774f2191937</t>
+          <t>https://www.indeed.com/viewjob?jk=9c24ee3772fb2025</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer- Local</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sidley Austin</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, GCP, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c24ee3772fb2025</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f567112b742a9e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer- Local</t>
+          <t>AWS Cloud Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f567112b742a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=e787928433fb38f9</t>
         </is>
       </c>
     </row>
@@ -748,87 +748,87 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Willdan</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
+          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4ce7bf4011426a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e02ba02243648f0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Integration Developer, Senior</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03b8bbec4a94a31c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c02ad439b17c3a6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Analyst / Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VantageScore</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12497ac075998e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac01b3454ac02ccf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Full Stack Developer &amp; Architect</t>
+          <t>Analyst / Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,137 +881,137 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1245fb4aa0b33840</t>
+          <t>https://www.indeed.com/viewjob?jk=d92003d1693fcf89</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Forward Deployed Engineer (Foundry)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Trinity Industries</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1207216093eb19</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4ce7bf4011426a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Integration Developer, Senior</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154aec3c659c637e</t>
+          <t>https://www.indeed.com/viewjob?jk=03b8bbec4a94a31c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VantageScore</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b763ccac8082bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=12497ac075998e0b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>AI Full Stack Developer &amp; Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f3215e173a2f079</t>
+          <t>https://www.indeed.com/viewjob?jk=1245fb4aa0b33840</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Sr Forward Deployed Engineer (Foundry)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Trinity Industries</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35019214a98b077</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1207216093eb19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9516aa524f738d9</t>
+          <t>https://www.indeed.com/viewjob?jk=154aec3c659c637e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5239019737c1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=7b763ccac8082bb3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>EMS Applications Developer Sr.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>ERCOT/Electric Reliability Council of Texas</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46cdeb4b1af72885</t>
+          <t>https://www.indeed.com/viewjob?jk=19fd76ad63566482</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688d23a37649aa4e</t>
+          <t>https://www.indeed.com/viewjob?jk=2f3215e173a2f079</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pharma Applications Engineer</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82dba2e1c1cad0d</t>
+          <t>https://www.indeed.com/viewjob?jk=a35019214a98b077</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,19 +1266,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c6986e7938de04</t>
+          <t>https://www.indeed.com/viewjob?jk=b9516aa524f738d9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Intregration Engineer</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IntegraTouch</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Cloud Storage, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189b52949d35286b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5239019737c1e6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, RDS, Azure, SQL Server, DynamoDB, Splunk</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eaa43d2708b0fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=46cdeb4b1af72885</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a198e2f00d09e497</t>
+          <t>https://www.indeed.com/viewjob?jk=688d23a37649aa4e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Pharma Applications Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5897cf20f4924d</t>
+          <t>https://www.indeed.com/viewjob?jk=f82dba2e1c1cad0d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6add22c42e86ee8d</t>
+          <t>https://www.indeed.com/viewjob?jk=cef42acc1d37c051</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=060e90baddbaabb6</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c6986e7938de04</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior Data Intregration Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>IntegraTouch</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, S3, Azure, GCP, Cloud Storage, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fa15772fc8215e</t>
+          <t>https://www.indeed.com/viewjob?jk=189b52949d35286b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior Database Engineer (AWS/Snowflake/Postgres)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,59 +1546,59 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbeaf5356928be79</t>
+          <t>https://www.indeed.com/viewjob?jk=4ea429cd1057282d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, RDS, Azure, SQL Server, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30aac5b70ec21742</t>
+          <t>https://www.indeed.com/viewjob?jk=1eaa43d2708b0fa5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>BCS Financial Corporation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1224f39b4d10142</t>
+          <t>https://www.indeed.com/viewjob?jk=16e946946005f3c9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Data and AI Quality Automation Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MySQL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b20c6e56d2f2685</t>
+          <t>https://www.indeed.com/viewjob?jk=471e912481eed840</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, Kinesis, Redshift, SQS, IAM, RDS, Oracle, MySQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57de84d9a0a356fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ff0504cd8c91e07a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Success Academy Charter Schools</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7a4bbc97a4a7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=f69cae0b073ffd83</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Deployment Engineer (Infrastructure &amp; DevOps)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Bedrock Data</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0d1d3131f74e61</t>
+          <t>https://www.indeed.com/viewjob?jk=73d8155dedb8c388</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Analyst - Data Engineering 5A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,102 +1791,102 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99acdc5f038ec993</t>
+          <t>https://www.indeed.com/viewjob?jk=b591868fadbb51ae</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>BIBA Practice - Big Data Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417fe7ce0dd45b13</t>
+          <t>https://www.indeed.com/viewjob?jk=2a35842ddaad367b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>GoodRx</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba18545223c64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=9da3eb1c099fc483</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Oracle Unity/Fusion Customer Data Platform (CDP) Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Hashout Technologies, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b7609618f1bb60b</t>
+          <t>https://www.indeed.com/viewjob?jk=05820054e138dd33</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42786522a873fac5</t>
+          <t>https://www.indeed.com/viewjob?jk=4de6845b355390df</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1e37739c6d4489</t>
+          <t>https://www.indeed.com/viewjob?jk=a89ce09999706a8d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4837b9e4911393cf</t>
+          <t>https://www.indeed.com/viewjob?jk=46f97f725c092d19</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7ab2808448b848</t>
+          <t>https://www.indeed.com/viewjob?jk=ef6f778294e73998</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Salesforce Enterprise Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Purple Austyn Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c440af126bc87e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef8a774183b65cc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Interworks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aed0004eb1e73c2</t>
+          <t>https://www.indeed.com/viewjob?jk=9d13d49983362928</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Interworks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e007bbdf452d21</t>
+          <t>https://www.indeed.com/viewjob?jk=8f63a609ce9a0e0e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Kafka, NoSQL, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b4f9cd182d1098</t>
+          <t>https://www.indeed.com/viewjob?jk=78ff4d06117e88a9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10812a5dd633ba29</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f1526a2cc9c583</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ketchikan, AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,312 +2246,312 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cbc2599ef10ec38</t>
+          <t>https://www.indeed.com/viewjob?jk=8f633477012d7720</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d3c03923d226d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a6ca2be8a3ba1c4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f0c53177d376165</t>
+          <t>https://www.indeed.com/viewjob?jk=66f736568439fa09</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb2d6450935c77c</t>
+          <t>https://www.indeed.com/viewjob?jk=d38e83f9c27ee7f1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2139a4cc82cf98d5</t>
+          <t>https://www.indeed.com/viewjob?jk=b1b55ac084d2b38e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ec6e1b6a41c09d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bedeff840282078</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a8660d20e3925c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d440465d091eb4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea946bc190711225</t>
+          <t>https://www.indeed.com/viewjob?jk=be9f49babb6ca927</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a44a6e66a933e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d474f9c4c5e446c7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Data Platform Architect, AI Adoption</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df6fdfb75f5432d</t>
+          <t>https://www.indeed.com/viewjob?jk=abf4cabe83b9851e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Site Reliability Engineer Remote - US • Remote</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Daxko</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, Scala, SQL Server, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9aa599a96ed4d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=612993f0cf902297</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>RA Capital Management</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68cdb549def54218</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb511c116964595</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior AI &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Alamar Biosciences</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>ECS, RDS, Databricks, Unity Catalog, BigQuery, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,102 +2666,102 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7272f84ff6357152</t>
+          <t>https://www.indeed.com/viewjob?jk=1884155644ac6742</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Lentech Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, Step Functions, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52db1fcf17eb0ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=326849a7cfebb04a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Harbinger Motors Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02b0fedb5c9b46f</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf02ed4b934745c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ccfe1a1c1f3d82</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c2350b85e1faca</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96157e562b62f43b</t>
+          <t>https://www.indeed.com/viewjob?jk=a9af2358984349df</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Genesys</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, S3, SQS, IAM, Scala, DynamoDB, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcfbe3b324a53aa8</t>
+          <t>https://www.indeed.com/viewjob?jk=be2a8db8df79df5f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Aerospace Software DevOps Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb0f2907c4f113d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b1191705b29853</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Nexstar Media Group, Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81bfbbc916c4bf3d</t>
+          <t>https://www.indeed.com/viewjob?jk=9158d7ecaabe631d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Nexstar Media Group, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,1232 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae070dd661915e6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Data Engineer (Remote)</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>FCT</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>OK, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=836c940883a7c623</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Data Engineer (Remote)</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>FCT</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>SC, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9623f5aff1bc8e49</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Data Engineer (Remote)</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>FCT</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d05fef2d9ced9478</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Data Engineer (Remote)</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>FCT</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>DE, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Talend</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d976dafe088343</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>BCS Financial Corporation</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16e946946005f3c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Data and AI Quality Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Stratus</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MySQL, ELT</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=471e912481eed840</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>AI Software Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Success Academy Charter Schools</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, BigQuery, Scala</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f69cae0b073ffd83</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Pacific Consulting</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afb97449b7ed7b0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Azure Data Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Desmata Inc</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Texas City, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Lake Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b018ddcc7ace0923</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>BIBA Practice - Big Data Architect</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Hexaware Technologies</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35842ddaad367b</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>GoodRx</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9da3eb1c099fc483</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Oracle Unity/Fusion Customer Data Platform (CDP) Developer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Hashout Technologies, Inc.</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=05820054e138dd33</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4de6845b355390df</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Santa Monica, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a89ce09999706a8d</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46f97f725c092d19</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6f778294e73998</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Salesforce Enterprise Architect</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Purple Austyn Technologies</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef8a774183b65cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Bain &amp; Company</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f1526a2cc9c583</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior .net Software Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f633477012d7720</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Sr Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Hertz</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6ca2be8a3ba1c4</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Bain &amp; Company</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=66f736568439fa09</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Bain &amp; Company</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d38e83f9c27ee7f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Bain &amp; Company</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b1b55ac084d2b38e</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Bain &amp; Company</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bedeff840282078</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Bain &amp; Company</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d440465d091eb4</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Data Platform Architect, AI Adoption</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Tesla</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=abf4cabe83b9851e</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>UT Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be9f49babb6ca927</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Database Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d474f9c4c5e446c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Data Solution Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>RA Capital Management</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb511c116964595</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior AI &amp; Data Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Alamar Biosciences</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Fremont, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Databricks, Unity Catalog, BigQuery, Snowflake, Data Modeling, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1884155644ac6742</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Lentech Inc.</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Fort Meade, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=326849a7cfebb04a</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Sr. Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Harbinger Motors Inc.</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Garden Grove, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf02ed4b934745c</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Genesys</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, IAM, Scala, DynamoDB, Jenkins, Maven, Jenkins</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be2a8db8df79df5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Aerospace Software DevOps Engineer II</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Blue Origin</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b1191705b29853</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>ServiceTitan</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab39fae8644125cb</t>
+          <t>https://www.indeed.com/viewjob?jk=746360ee3987922f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-19.xlsx
+++ b/results/job_matches_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer- Local</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sidley Austin</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, GCP, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c24ee3772fb2025</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f567112b742a9e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer- Local</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, GCP, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f567112b742a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=9c24ee3772fb2025</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AI Full Stack Developer &amp; Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VantageScore</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, CI/CD</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12497ac075998e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=1245fb4aa0b33840</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Full Stack Developer &amp; Architect</t>
+          <t>Sr Forward Deployed Engineer (Foundry)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>Trinity Industries</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1245fb4aa0b33840</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1207216093eb19</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Forward Deployed Engineer (Foundry)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Trinity Industries</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1207216093eb19</t>
+          <t>https://www.indeed.com/viewjob?jk=154aec3c659c637e</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154aec3c659c637e</t>
+          <t>https://www.indeed.com/viewjob?jk=7b763ccac8082bb3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b763ccac8082bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f3215e173a2f079</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EMS Applications Developer Sr.</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ERCOT/Electric Reliability Council of Texas</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19fd76ad63566482</t>
+          <t>https://www.indeed.com/viewjob?jk=a35019214a98b077</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f3215e173a2f079</t>
+          <t>https://www.indeed.com/viewjob?jk=b9516aa524f738d9</t>
         </is>
       </c>
     </row>
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35019214a98b077</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5239019737c1e6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>Google Cloud Platform, GCP, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9516aa524f738d9</t>
+          <t>https://www.indeed.com/viewjob?jk=28e1c461015035ce</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Encino, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5239019737c1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=b5196076aab88a07</t>
         </is>
       </c>
     </row>
@@ -1378,35 +1378,35 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pharma Applications Engineer</t>
+          <t>Senior Azure Data Engineer (W2 only)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Highbrow Technology Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82dba2e1c1cad0d</t>
+          <t>https://www.indeed.com/viewjob?jk=3be2ecbf806de066</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data and AI Quality Automation Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MySQL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471e912481eed840</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c60daa2eb488c</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BIBA Practice - Big Data Architect</t>
+          <t>MLOps Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35842ddaad367b</t>
+          <t>https://www.indeed.com/viewjob?jk=04c53274a80c0bed</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GoodRx</t>
+          <t>Cloud Aviation</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>El Monte, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,29 +1851,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da3eb1c099fc483</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecef5b286b3de60</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Oracle Unity/Fusion Customer Data Platform (CDP) Developer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hashout Technologies, Inc.</t>
+          <t>GoodRx</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1886,42 +1886,42 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05820054e138dd33</t>
+          <t>https://www.indeed.com/viewjob?jk=9da3eb1c099fc483</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de6845b355390df</t>
+          <t>https://www.indeed.com/viewjob?jk=d10eba39e5e728f7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89ce09999706a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=553af7a9ea2c94ac</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clarita, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f97f725c092d19</t>
+          <t>https://www.indeed.com/viewjob?jk=9008cdf9aec7fb4b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6f778294e73998</t>
+          <t>https://www.indeed.com/viewjob?jk=b372a3e7801d9f67</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Salesforce Enterprise Architect</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Purple Austyn Technologies</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef8a774183b65cc</t>
+          <t>https://www.indeed.com/viewjob?jk=d45b94dc1f208983</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Analytics Architect</t>
+          <t>Oracle Unity/Fusion Customer Data Platform (CDP) Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Interworks</t>
+          <t>Hashout Technologies, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d13d49983362928</t>
+          <t>https://www.indeed.com/viewjob?jk=05820054e138dd33</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Analytics Architect</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Interworks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f63a609ce9a0e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=a89ce09999706a8d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Kafka, NoSQL, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ff4d06117e88a9</t>
+          <t>https://www.indeed.com/viewjob?jk=46f97f725c092d19</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f1526a2cc9c583</t>
+          <t>https://www.indeed.com/viewjob?jk=ef6f778294e73998</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f633477012d7720</t>
+          <t>https://www.indeed.com/viewjob?jk=4de6845b355390df</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>Technical Architect (BIBA)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Snowflake, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6ca2be8a3ba1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc844d637a4a899</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>AWS, Glue, Azure, GCP, Cloud Storage, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f736568439fa09</t>
+          <t>https://www.indeed.com/viewjob?jk=07961822c801c505</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer II -- Enterprise AI Products Value Stream</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38e83f9c27ee7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=72ccfb0ea0091329</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Kafka, NoSQL, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1b55ac084d2b38e</t>
+          <t>https://www.indeed.com/viewjob?jk=78ff4d06117e88a9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Interworks</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bedeff840282078</t>
+          <t>https://www.indeed.com/viewjob?jk=9d13d49983362928</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Interworks</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d440465d091eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=8f63a609ce9a0e0e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>Salesforce Enterprise Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Purple Austyn Technologies</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9f49babb6ca927</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef8a774183b65cc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d474f9c4c5e446c7</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f1526a2cc9c583</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Platform Architect, AI Adoption</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf4cabe83b9851e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f633477012d7720</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer Remote - US • Remote</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Daxko</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,182 +2586,182 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Scala, SQL Server, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612993f0cf902297</t>
+          <t>https://www.indeed.com/viewjob?jk=66f736568439fa09</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RA Capital Management</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb511c116964595</t>
+          <t>https://www.indeed.com/viewjob?jk=d38e83f9c27ee7f1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Alamar Biosciences</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Unity Catalog, BigQuery, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1884155644ac6742</t>
+          <t>https://www.indeed.com/viewjob?jk=b1b55ac084d2b38e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lentech Inc.</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Terraform, Git</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326849a7cfebb04a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bedeff840282078</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Harbinger Motors Inc.</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf02ed4b934745c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d440465d091eb4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer</t>
+          <t>Data Platform Architect, AI Adoption</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c2350b85e1faca</t>
+          <t>https://www.indeed.com/viewjob?jk=abf4cabe83b9851e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9af2358984349df</t>
+          <t>https://www.indeed.com/viewjob?jk=be9f49babb6ca927</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability Engineer Remote - US • Remote</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Genesys</t>
+          <t>Daxko</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, IAM, Scala, DynamoDB, Jenkins, Maven, Jenkins</t>
+          <t>AWS, Scala, SQL Server, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be2a8db8df79df5f</t>
+          <t>https://www.indeed.com/viewjob?jk=612993f0cf902297</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Aerospace Software DevOps Engineer II</t>
+          <t>Senior Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b1191705b29853</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c2350b85e1faca</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nexstar Media Group, Inc.</t>
+          <t>RA Capital Management</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9158d7ecaabe631d</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb511c116964595</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior AI &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nexstar Media Group, Inc.</t>
+          <t>Alamar Biosciences</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,15 +2936,120 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>ECS, RDS, Databricks, Unity Catalog, BigQuery, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1884155644ac6742</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Aerospace Software DevOps Engineer II</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Blue Origin</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2b1191705b29853</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Nexstar Media Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9158d7ecaabe631d</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Nexstar Media Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=746360ee3987922f</t>
         </is>
